--- a/数据对比/普通选手各赛段数据.xlsx
+++ b/数据对比/普通选手各赛段数据.xlsx
@@ -210,12 +210,12 @@
         <t>该次比赛具有有效 Games 和 Dmg dealt 数据的参赛选手数。</t>
       </text>
     </comment>
-    <comment ref="N10" authorId="0" shapeId="0">
+    <comment ref="N11" authorId="0" shapeId="0">
       <text>
         <t>按该次比赛全部参赛选手的 Dmg dealt / Games 降序排名。</t>
       </text>
     </comment>
-    <comment ref="O10" authorId="0" shapeId="0">
+    <comment ref="O11" authorId="0" shapeId="0">
       <text>
         <t>该次比赛具有有效 Games 和 Dmg dealt 数据的参赛选手数。</t>
       </text>
@@ -240,12 +240,12 @@
         <t>该次比赛具有有效 Games 和 Dmg dealt 数据的参赛选手数。</t>
       </text>
     </comment>
-    <comment ref="N11" authorId="0" shapeId="0">
+    <comment ref="N12" authorId="0" shapeId="0">
       <text>
         <t>按该次比赛全部参赛选手的 Dmg dealt / Games 降序排名。</t>
       </text>
     </comment>
-    <comment ref="O11" authorId="0" shapeId="0">
+    <comment ref="O12" authorId="0" shapeId="0">
       <text>
         <t>该次比赛具有有效 Games 和 Dmg dealt 数据的参赛选手数。</t>
       </text>
@@ -300,6 +300,36 @@
         <t>该次比赛具有有效 Games 和 Dmg dealt 数据的参赛选手数。</t>
       </text>
     </comment>
+    <comment ref="N12" authorId="0" shapeId="0">
+      <text>
+        <t>按该次比赛全部参赛选手的 Dmg dealt / Games 降序排名。</t>
+      </text>
+    </comment>
+    <comment ref="O12" authorId="0" shapeId="0">
+      <text>
+        <t>该次比赛具有有效 Games 和 Dmg dealt 数据的参赛选手数。</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Codex</author>
+  </authors>
+  <commentList>
+    <comment ref="N2" authorId="0" shapeId="0">
+      <text>
+        <t>按该次比赛全部参赛选手的 Dmg dealt / Games 降序排名。</t>
+      </text>
+    </comment>
+    <comment ref="O2" authorId="0" shapeId="0">
+      <text>
+        <t>该次比赛具有有效 Games 和 Dmg dealt 数据的参赛选手数。</t>
+      </text>
+    </comment>
     <comment ref="N11" authorId="0" shapeId="0">
       <text>
         <t>按该次比赛全部参赛选手的 Dmg dealt / Games 降序排名。</t>
@@ -314,7 +344,7 @@
 </comments>
 </file>
 
-<file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments/comment4.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Codex</author>
@@ -344,7 +374,7 @@
 </comments>
 </file>
 
-<file path=xl/comments/comment4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments/comment5.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Codex</author>
@@ -360,12 +390,12 @@
         <t>该次比赛具有有效 Games 和 Dmg dealt 数据的参赛选手数。</t>
       </text>
     </comment>
-    <comment ref="N9" authorId="0" shapeId="0">
+    <comment ref="N12" authorId="0" shapeId="0">
       <text>
         <t>按该次比赛全部参赛选手的 Dmg dealt / Games 降序排名。</t>
       </text>
     </comment>
-    <comment ref="O9" authorId="0" shapeId="0">
+    <comment ref="O12" authorId="0" shapeId="0">
       <text>
         <t>该次比赛具有有效 Games 和 Dmg dealt 数据的参赛选手数。</t>
       </text>
@@ -374,7 +404,7 @@
 </comments>
 </file>
 
-<file path=xl/comments/comment5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments/comment6.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Codex</author>
@@ -404,36 +434,6 @@
 </comments>
 </file>
 
-<file path=xl/comments/comment6.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Codex</author>
-  </authors>
-  <commentList>
-    <comment ref="N2" authorId="0" shapeId="0">
-      <text>
-        <t>按该次比赛全部参赛选手的 Dmg dealt / Games 降序排名。</t>
-      </text>
-    </comment>
-    <comment ref="O2" authorId="0" shapeId="0">
-      <text>
-        <t>该次比赛具有有效 Games 和 Dmg dealt 数据的参赛选手数。</t>
-      </text>
-    </comment>
-    <comment ref="N10" authorId="0" shapeId="0">
-      <text>
-        <t>按该次比赛全部参赛选手的 Dmg dealt / Games 降序排名。</t>
-      </text>
-    </comment>
-    <comment ref="O10" authorId="0" shapeId="0">
-      <text>
-        <t>该次比赛具有有效 Games 和 Dmg dealt 数据的参赛选手数。</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/comments/comment7.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
@@ -450,12 +450,12 @@
         <t>该次比赛具有有效 Games 和 Dmg dealt 数据的参赛选手数。</t>
       </text>
     </comment>
-    <comment ref="N7" authorId="0" shapeId="0">
+    <comment ref="N8" authorId="0" shapeId="0">
       <text>
         <t>按该次比赛全部参赛选手的 Dmg dealt / Games 降序排名。</t>
       </text>
     </comment>
-    <comment ref="O7" authorId="0" shapeId="0">
+    <comment ref="O8" authorId="0" shapeId="0">
       <text>
         <t>该次比赛具有有效 Games 和 Dmg dealt 数据的参赛选手数。</t>
       </text>
@@ -510,12 +510,12 @@
         <t>该次比赛具有有效 Games 和 Dmg dealt 数据的参赛选手数。</t>
       </text>
     </comment>
-    <comment ref="N11" authorId="0" shapeId="0">
+    <comment ref="N12" authorId="0" shapeId="0">
       <text>
         <t>按该次比赛全部参赛选手的 Dmg dealt / Games 降序排名。</t>
       </text>
     </comment>
-    <comment ref="O11" authorId="0" shapeId="0">
+    <comment ref="O12" authorId="0" shapeId="0">
       <text>
         <t>该次比赛具有有效 Games 和 Dmg dealt 数据的参赛选手数。</t>
       </text>
@@ -525,8 +525,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PiteRegularSeasonStats" displayName="PiteRegularSeasonStats" ref="A2:O7" headerRowCount="1">
-  <autoFilter ref="A2:O7"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PiteRegularSeasonStats" displayName="PiteRegularSeasonStats" ref="A2:O8" headerRowCount="1">
+  <autoFilter ref="A2:O8"/>
   <tableColumns count="15">
     <tableColumn id="1" name="赛段"/>
     <tableColumn id="2" name="选手"/>
@@ -549,8 +549,8 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="Player5World" displayName="Player5World" ref="A11:O14" headerRowCount="1">
-  <autoFilter ref="A11:O14"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="Player5World" displayName="Player5World" ref="A12:O15" headerRowCount="1">
+  <autoFilter ref="A12:O15"/>
   <tableColumns count="15">
     <tableColumn id="1" name="赛段"/>
     <tableColumn id="2" name="选手"/>
@@ -573,8 +573,8 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="Player6Regular" displayName="Player6Regular" ref="A2:O7" headerRowCount="1">
-  <autoFilter ref="A2:O7"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="Player6Regular" displayName="Player6Regular" ref="A2:O8" headerRowCount="1">
+  <autoFilter ref="A2:O8"/>
   <tableColumns count="15">
     <tableColumn id="1" name="赛段"/>
     <tableColumn id="2" name="选手"/>
@@ -597,8 +597,8 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="Player6World" displayName="Player6World" ref="A10:O14" headerRowCount="1">
-  <autoFilter ref="A10:O14"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="Player6World" displayName="Player6World" ref="A11:O15" headerRowCount="1">
+  <autoFilter ref="A11:O15"/>
   <tableColumns count="15">
     <tableColumn id="1" name="赛段"/>
     <tableColumn id="2" name="选手"/>
@@ -621,8 +621,8 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="Player7Regular" displayName="Player7Regular" ref="A2:O4" headerRowCount="1">
-  <autoFilter ref="A2:O4"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="Player7Regular" displayName="Player7Regular" ref="A2:O5" headerRowCount="1">
+  <autoFilter ref="A2:O5"/>
   <tableColumns count="15">
     <tableColumn id="1" name="赛段"/>
     <tableColumn id="2" name="选手"/>
@@ -645,8 +645,8 @@
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="Player7World" displayName="Player7World" ref="A7:O8" headerRowCount="1">
-  <autoFilter ref="A7:O8"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="Player7World" displayName="Player7World" ref="A8:O9" headerRowCount="1">
+  <autoFilter ref="A8:O9"/>
   <tableColumns count="15">
     <tableColumn id="1" name="赛段"/>
     <tableColumn id="2" name="选手"/>
@@ -717,8 +717,8 @@
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="17" name="Player9Regular" displayName="Player9Regular" ref="A2:O8" headerRowCount="1">
-  <autoFilter ref="A2:O8"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="17" name="Player9Regular" displayName="Player9Regular" ref="A2:O9" headerRowCount="1">
+  <autoFilter ref="A2:O9"/>
   <tableColumns count="15">
     <tableColumn id="1" name="赛段"/>
     <tableColumn id="2" name="选手"/>
@@ -741,8 +741,8 @@
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="18" name="Player9World" displayName="Player9World" ref="A11:O15" headerRowCount="1">
-  <autoFilter ref="A11:O15"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="18" name="Player9World" displayName="Player9World" ref="A12:O16" headerRowCount="1">
+  <autoFilter ref="A12:O16"/>
   <tableColumns count="15">
     <tableColumn id="1" name="赛段"/>
     <tableColumn id="2" name="选手"/>
@@ -765,8 +765,8 @@
 </file>
 
 <file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="Player10Regular" displayName="Player10Regular" ref="A2:O8" headerRowCount="1">
-  <autoFilter ref="A2:O8"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="Player10Regular" displayName="Player10Regular" ref="A2:O9" headerRowCount="1">
+  <autoFilter ref="A2:O9"/>
   <tableColumns count="15">
     <tableColumn id="1" name="赛段"/>
     <tableColumn id="2" name="选手"/>
@@ -789,8 +789,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="PiteWorldEventStats" displayName="PiteWorldEventStats" ref="A10:O16" headerRowCount="1">
-  <autoFilter ref="A10:O16"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="PiteWorldEventStats" displayName="PiteWorldEventStats" ref="A11:O17" headerRowCount="1">
+  <autoFilter ref="A11:O17"/>
   <tableColumns count="15">
     <tableColumn id="1" name="赛段"/>
     <tableColumn id="2" name="选手"/>
@@ -813,8 +813,8 @@
 </file>
 
 <file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="Player10World" displayName="Player10World" ref="A11:O15" headerRowCount="1">
-  <autoFilter ref="A11:O15"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="Player10World" displayName="Player10World" ref="A12:O16" headerRowCount="1">
+  <autoFilter ref="A12:O16"/>
   <tableColumns count="15">
     <tableColumn id="1" name="赛段"/>
     <tableColumn id="2" name="选手"/>
@@ -861,7 +861,55 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="KassaRegularSeasonStats" displayName="KassaRegularSeasonStats" ref="A2:O8" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="KassaRegularSeasonStats" displayName="KassaRegularSeasonStats" ref="A2:O9" headerRowCount="1">
+  <autoFilter ref="A2:O9"/>
+  <tableColumns count="15">
+    <tableColumn id="1" name="赛段"/>
+    <tableColumn id="2" name="选手"/>
+    <tableColumn id="3" name="Games"/>
+    <tableColumn id="4" name="Kills"/>
+    <tableColumn id="5" name="Assists"/>
+    <tableColumn id="6" name="Deaths"/>
+    <tableColumn id="7" name="KA/D"/>
+    <tableColumn id="8" name="Dmg dealt"/>
+    <tableColumn id="9" name="Dmg taken"/>
+    <tableColumn id="10" name="Dmg diff"/>
+    <tableColumn id="11" name="Dmg dealt/Games"/>
+    <tableColumn id="12" name="Carry Value"/>
+    <tableColumn id="13" name="Player Value"/>
+    <tableColumn id="14" name="场均伤害排名（本次比赛）"/>
+    <tableColumn id="15" name="参赛选手人数"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="KassaWorldEventStats" displayName="KassaWorldEventStats" ref="A12:O18" headerRowCount="1">
+  <autoFilter ref="A12:O18"/>
+  <tableColumns count="15">
+    <tableColumn id="1" name="赛段"/>
+    <tableColumn id="2" name="选手"/>
+    <tableColumn id="3" name="Games"/>
+    <tableColumn id="4" name="Kills"/>
+    <tableColumn id="5" name="Assists"/>
+    <tableColumn id="6" name="Deaths"/>
+    <tableColumn id="7" name="KA/D"/>
+    <tableColumn id="8" name="Dmg dealt"/>
+    <tableColumn id="9" name="Dmg taken"/>
+    <tableColumn id="10" name="Dmg diff"/>
+    <tableColumn id="11" name="Dmg dealt/Games"/>
+    <tableColumn id="12" name="Carry Value"/>
+    <tableColumn id="13" name="Player Value"/>
+    <tableColumn id="14" name="场均伤害排名（本次比赛）"/>
+    <tableColumn id="15" name="参赛选手人数"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Player3Regular" displayName="Player3Regular" ref="A2:O8" headerRowCount="1">
   <autoFilter ref="A2:O8"/>
   <tableColumns count="15">
     <tableColumn id="1" name="赛段"/>
@@ -884,9 +932,9 @@
 </table>
 </file>
 
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="KassaWorldEventStats" displayName="KassaWorldEventStats" ref="A11:O17" headerRowCount="1">
-  <autoFilter ref="A11:O17"/>
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Player3World" displayName="Player3World" ref="A11:O18" headerRowCount="1">
+  <autoFilter ref="A11:O18"/>
   <tableColumns count="15">
     <tableColumn id="1" name="赛段"/>
     <tableColumn id="2" name="选手"/>
@@ -908,8 +956,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Player3Regular" displayName="Player3Regular" ref="A2:O7" headerRowCount="1">
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Player4Regular" displayName="Player4Regular" ref="A2:O7" headerRowCount="1">
   <autoFilter ref="A2:O7"/>
   <tableColumns count="15">
     <tableColumn id="1" name="赛段"/>
@@ -932,57 +980,9 @@
 </table>
 </file>
 
-<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Player3World" displayName="Player3World" ref="A10:O17" headerRowCount="1">
-  <autoFilter ref="A10:O17"/>
-  <tableColumns count="15">
-    <tableColumn id="1" name="赛段"/>
-    <tableColumn id="2" name="选手"/>
-    <tableColumn id="3" name="Games"/>
-    <tableColumn id="4" name="Kills"/>
-    <tableColumn id="5" name="Assists"/>
-    <tableColumn id="6" name="Deaths"/>
-    <tableColumn id="7" name="KA/D"/>
-    <tableColumn id="8" name="Dmg dealt"/>
-    <tableColumn id="9" name="Dmg taken"/>
-    <tableColumn id="10" name="Dmg diff"/>
-    <tableColumn id="11" name="Dmg dealt/Games"/>
-    <tableColumn id="12" name="Carry Value"/>
-    <tableColumn id="13" name="Player Value"/>
-    <tableColumn id="14" name="场均伤害排名（本次比赛）"/>
-    <tableColumn id="15" name="参赛选手人数"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Player4Regular" displayName="Player4Regular" ref="A2:O6" headerRowCount="1">
-  <autoFilter ref="A2:O6"/>
-  <tableColumns count="15">
-    <tableColumn id="1" name="赛段"/>
-    <tableColumn id="2" name="选手"/>
-    <tableColumn id="3" name="Games"/>
-    <tableColumn id="4" name="Kills"/>
-    <tableColumn id="5" name="Assists"/>
-    <tableColumn id="6" name="Deaths"/>
-    <tableColumn id="7" name="KA/D"/>
-    <tableColumn id="8" name="Dmg dealt"/>
-    <tableColumn id="9" name="Dmg taken"/>
-    <tableColumn id="10" name="Dmg diff"/>
-    <tableColumn id="11" name="Dmg dealt/Games"/>
-    <tableColumn id="12" name="Carry Value"/>
-    <tableColumn id="13" name="Player Value"/>
-    <tableColumn id="14" name="场均伤害排名（本次比赛）"/>
-    <tableColumn id="15" name="参赛选手人数"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="Player4World" displayName="Player4World" ref="A9:O14" headerRowCount="1">
-  <autoFilter ref="A9:O14"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="Player4World" displayName="Player4World" ref="A10:O15" headerRowCount="1">
+  <autoFilter ref="A10:O15"/>
   <tableColumns count="15">
     <tableColumn id="1" name="赛段"/>
     <tableColumn id="2" name="选手"/>
@@ -1005,8 +1005,8 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="Player5Regular" displayName="Player5Regular" ref="A2:O8" headerRowCount="1">
-  <autoFilter ref="A2:O8"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="Player5Regular" displayName="Player5Regular" ref="A2:O9" headerRowCount="1">
+  <autoFilter ref="A2:O9"/>
   <tableColumns count="15">
     <tableColumn id="1" name="赛段"/>
     <tableColumn id="2" name="选手"/>
@@ -1317,7 +1317,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O18"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1676,145 +1676,145 @@
         <v>97</v>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="1" t="inlineStr">
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>APAC-S Y6-Split2</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Pite</t>
+        </is>
+      </c>
+      <c r="C8" s="5">
+        <v>45</v>
+      </c>
+      <c r="D8" s="5">
+        <v>68</v>
+      </c>
+      <c r="E8" s="5">
+        <v>57</v>
+      </c>
+      <c r="F8" s="5">
+        <v>48</v>
+      </c>
+      <c r="G8" s="6">
+        <v>2.6041666666666665</v>
+      </c>
+      <c r="H8" s="5">
+        <v>32958</v>
+      </c>
+      <c r="I8" s="5">
+        <v>27908</v>
+      </c>
+      <c r="J8" s="5">
+        <v>5050</v>
+      </c>
+      <c r="K8" s="6">
+        <v>732.4</v>
+      </c>
+      <c r="L8" s="6">
+        <v>1.2</v>
+      </c>
+      <c r="M8" s="6">
+        <v>24.35</v>
+      </c>
+      <c r="N8" s="5">
+        <v>30</v>
+      </c>
+      <c r="O8" s="5">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="10" ht="34" customHeight="1">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>Pite 世界赛数据</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="11" ht="34" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>赛段</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>选手</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>Games</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Kills</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Assists</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Deaths</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>KA/D</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Dmg dealt</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>Dmg taken</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>Dmg diff</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>Dmg dealt/Games</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>Carry Value</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>Player Value</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>场均伤害排名（本次比赛）</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>参赛选手人数</t>
         </is>
-      </c>
-    </row>
-    <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Y3-S2 Playoffs</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Pite</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="D11" s="5" t="n">
-        <v>31</v>
-      </c>
-      <c r="E11" s="5" t="n">
-        <v>34</v>
-      </c>
-      <c r="F11" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="G11" s="6" t="n">
-        <v>2.166666666666667</v>
-      </c>
-      <c r="H11" s="5" t="n">
-        <v>17277</v>
-      </c>
-      <c r="I11" s="5" t="n">
-        <v>15564</v>
-      </c>
-      <c r="J11" s="5" t="n">
-        <v>1713</v>
-      </c>
-      <c r="K11" s="6" t="n">
-        <v>575.9</v>
-      </c>
-      <c r="L11" s="6" t="n">
-        <v>-1.53</v>
-      </c>
-      <c r="M11" s="6" t="n">
-        <v>7.83</v>
-      </c>
-      <c r="N11" s="5" t="n">
-        <v>51</v>
-      </c>
-      <c r="O11" s="5" t="n">
-        <v>122</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Y3-Championship</t>
+          <t>Y3-S2 Playoffs</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -1823,49 +1823,49 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="E12" s="5" t="n">
         <v>34</v>
       </c>
-      <c r="D12" s="5" t="n">
-        <v>37</v>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>40</v>
-      </c>
       <c r="F12" s="5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>2.655172413793104</v>
+        <v>2.166666666666667</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>23310</v>
+        <v>17277</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>17298</v>
+        <v>15564</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>6012</v>
+        <v>1713</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>685.5882352941177</v>
+        <v>575.9</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>-3.94</v>
+        <v>-1.53</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>27.86</v>
+        <v>7.83</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="O12" s="5" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Y4-S2 Playoffs</t>
+          <t>Y3-Championship</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -1874,49 +1874,49 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="E13" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="D13" s="5" t="n">
-        <v>33</v>
-      </c>
-      <c r="E13" s="5" t="n">
-        <v>25</v>
-      </c>
       <c r="F13" s="5" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>1.526315789473684</v>
+        <v>2.655172413793104</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>17665</v>
+        <v>23310</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>19620</v>
+        <v>17298</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>-1955</v>
+        <v>6012</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>441.625</v>
+        <v>685.5882352941177</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>-29.91</v>
+        <v>-3.94</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>-16.5</v>
+        <v>27.86</v>
       </c>
       <c r="N13" s="5" t="n">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="O13" s="5" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Y4-Championship</t>
+          <t>Y4-S2 Playoffs</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -1925,49 +1925,49 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>1.307692307692308</v>
+        <v>1.526315789473684</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>10761</v>
+        <v>17665</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>12198</v>
+        <v>19620</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>-1437</v>
+        <v>-1955</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>413.8846153846154</v>
+        <v>441.625</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>-28.97</v>
+        <v>-29.91</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>-40.93</v>
+        <v>-16.5</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>118</v>
+        <v>91</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Y5-S1 Playoffs/EWC</t>
+          <t>Y4-Championship</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -1976,40 +1976,40 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>1.2</v>
+        <v>1.307692307692308</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>4278</v>
+        <v>10761</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>5781</v>
+        <v>12198</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>-1503</v>
+        <v>-1437</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>427.8</v>
+        <v>413.8846153846154</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>20.71</v>
+        <v>-28.97</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>-22.41</v>
+        <v>-40.93</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="O15" s="5" t="n">
         <v>120</v>
@@ -2018,56 +2018,107 @@
     <row r="16" ht="24" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
+          <t>Y5-S1 Playoffs/EWC</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Pite</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>4278</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>5781</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>-1503</v>
+      </c>
+      <c r="K16" s="6" t="n">
+        <v>427.8</v>
+      </c>
+      <c r="L16" s="6" t="n">
+        <v>20.71</v>
+      </c>
+      <c r="M16" s="6" t="n">
+        <v>-22.41</v>
+      </c>
+      <c r="N16" s="5" t="n">
+        <v>103</v>
+      </c>
+      <c r="O16" s="5" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
           <t>Y6-S1 Playoffs</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Pite</t>
         </is>
       </c>
-      <c r="C16" s="5" t="n">
+      <c r="C17" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="D16" s="5" t="n">
+      <c r="D17" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="E16" s="5" t="n">
+      <c r="E17" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="F16" s="5" t="n">
+      <c r="F17" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="G16" s="6" t="n">
+      <c r="G17" s="6" t="n">
         <v>1.666666666666667</v>
       </c>
-      <c r="H16" s="5" t="n">
+      <c r="H17" s="5" t="n">
         <v>20199</v>
       </c>
-      <c r="I16" s="5" t="n">
+      <c r="I17" s="5" t="n">
         <v>20487</v>
       </c>
-      <c r="J16" s="5" t="n">
+      <c r="J17" s="5" t="n">
         <v>-288</v>
       </c>
-      <c r="K16" s="6" t="n">
+      <c r="K17" s="6" t="n">
         <v>721.3928571428571</v>
       </c>
-      <c r="L16" s="6" t="n">
+      <c r="L17" s="6" t="n">
         <v>9.23</v>
       </c>
-      <c r="M16" s="6" t="n">
+      <c r="M17" s="6" t="n">
         <v>-1.75</v>
       </c>
-      <c r="N16" s="5" t="n">
+      <c r="N17" s="5" t="n">
         <v>57</v>
       </c>
-      <c r="O16" s="5" t="n">
+      <c r="O17" s="5" t="n">
         <v>121</v>
       </c>
     </row>
-    <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>排名口径：按每个赛段该次比赛的全部参赛选手，以累计伤害 / Games 计算场均伤害并降序排名。</t>
         </is>
@@ -2076,8 +2127,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A9:O9"/>
-    <mergeCell ref="A18:O18"/>
+    <mergeCell ref="A10:O10"/>
+    <mergeCell ref="A19:O19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -2094,7 +2145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -2504,145 +2555,145 @@
         <v>97</v>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
-      <c r="A10" s="1" t="inlineStr">
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>APAC-S Y6-Split2</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>JR</t>
+        </is>
+      </c>
+      <c r="C9" s="5">
+        <v>45</v>
+      </c>
+      <c r="D9" s="5">
+        <v>71</v>
+      </c>
+      <c r="E9" s="5">
+        <v>58</v>
+      </c>
+      <c r="F9" s="5">
+        <v>47</v>
+      </c>
+      <c r="G9" s="6">
+        <v>2.74468085106383</v>
+      </c>
+      <c r="H9" s="5">
+        <v>54411</v>
+      </c>
+      <c r="I9" s="5">
+        <v>34006</v>
+      </c>
+      <c r="J9" s="5">
+        <v>20405</v>
+      </c>
+      <c r="K9" s="6">
+        <v>1209.1333333333334</v>
+      </c>
+      <c r="L9" s="6">
+        <v>44.69</v>
+      </c>
+      <c r="M9" s="6">
+        <v>64.33</v>
+      </c>
+      <c r="N9" s="5">
+        <v>1</v>
+      </c>
+      <c r="O9" s="5">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="11" ht="34" customHeight="1">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>JR 世界赛数据</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="12" ht="34" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>赛段</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>选手</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Games</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Kills</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Assists</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Deaths</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>KA/D</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Dmg dealt</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>Dmg taken</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>Dmg diff</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>Dmg dealt/Games</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>Carry Value</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>Player Value</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>场均伤害排名（本次比赛）</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>参赛选手人数</t>
         </is>
-      </c>
-    </row>
-    <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Y4-S2 Playoffs</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>JR</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="n">
-        <v>24</v>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="G12" s="6" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="H12" s="5" t="n">
-        <v>10116</v>
-      </c>
-      <c r="I12" s="5" t="n">
-        <v>11044</v>
-      </c>
-      <c r="J12" s="5" t="n">
-        <v>-928</v>
-      </c>
-      <c r="K12" s="6" t="n">
-        <v>421.5</v>
-      </c>
-      <c r="L12" s="6" t="n">
-        <v>15.98</v>
-      </c>
-      <c r="M12" s="6" t="n">
-        <v>-22.18</v>
-      </c>
-      <c r="N12" s="5" t="n">
-        <v>98</v>
-      </c>
-      <c r="O12" s="5" t="n">
-        <v>123</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Y4-Championship</t>
+          <t>Y4-S2 Playoffs</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -2651,49 +2702,49 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>1.846153846153846</v>
+        <v>1.08</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>23633</v>
+        <v>10116</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>21762</v>
+        <v>11044</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>1871</v>
+        <v>-928</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>908.9615384615385</v>
+        <v>421.5</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>27.21</v>
+        <v>15.98</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>15.04</v>
+        <v>-22.18</v>
       </c>
       <c r="N13" s="5" t="n">
-        <v>18</v>
+        <v>98</v>
       </c>
       <c r="O13" s="5" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Y5-S1 Playoffs/EWC</t>
+          <t>Y4-Championship</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -2702,40 +2753,40 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D14" s="5" t="n">
         <v>26</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>1.954545454545455</v>
+        <v>1.846153846153846</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>14971</v>
+        <v>23633</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>10845</v>
+        <v>21762</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>4126</v>
+        <v>1871</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>748.55</v>
+        <v>908.9615384615385</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>34.09</v>
+        <v>27.21</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>23.64</v>
+        <v>15.04</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O14" s="5" t="n">
         <v>120</v>
@@ -2744,7 +2795,7 @@
     <row r="15" ht="24" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Y5-Championship</t>
+          <t>Y5-S1 Playoffs/EWC</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -2753,47 +2804,98 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>0.6538461538461539</v>
+        <v>1.954545454545455</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>13990</v>
+        <v>14971</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>16409</v>
+        <v>10845</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>-2419</v>
+        <v>4126</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>582.9166666666666</v>
+        <v>748.55</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>18.81</v>
+        <v>34.09</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>-22.43</v>
+        <v>23.64</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>80</v>
+        <v>23</v>
       </c>
       <c r="O15" s="5" t="n">
         <v>120</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Y5-Championship</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>JR</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.6538461538461539</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>13990</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>16409</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>-2419</v>
+      </c>
+      <c r="K16" s="6" t="n">
+        <v>582.9166666666666</v>
+      </c>
+      <c r="L16" s="6" t="n">
+        <v>18.81</v>
+      </c>
+      <c r="M16" s="6" t="n">
+        <v>-22.43</v>
+      </c>
+      <c r="N16" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="O16" s="5" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>排名口径：按每个赛段该次比赛的全部参赛选手，以累计伤害 / Games 计算场均伤害并降序排名。</t>
         </is>
@@ -2801,9 +2903,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A10:O10"/>
+    <mergeCell ref="A11:O11"/>
     <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A17:O17"/>
+    <mergeCell ref="A18:O18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -3188,7 +3290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:O20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -3598,145 +3700,145 @@
         <v>97</v>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
-      <c r="A10" s="1" t="inlineStr">
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>APAC-S Y6-Split2</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Kassa</t>
+        </is>
+      </c>
+      <c r="C9" s="5">
+        <v>45</v>
+      </c>
+      <c r="D9" s="5">
+        <v>28</v>
+      </c>
+      <c r="E9" s="5">
+        <v>59</v>
+      </c>
+      <c r="F9" s="5">
+        <v>46</v>
+      </c>
+      <c r="G9" s="6">
+        <v>1.891304347826087</v>
+      </c>
+      <c r="H9" s="5">
+        <v>24506</v>
+      </c>
+      <c r="I9" s="5">
+        <v>27633</v>
+      </c>
+      <c r="J9" s="5">
+        <v>-3127</v>
+      </c>
+      <c r="K9" s="6">
+        <v>544.5777777777778</v>
+      </c>
+      <c r="L9" s="6">
+        <v>-77.32</v>
+      </c>
+      <c r="M9" s="6">
+        <v>-17.01</v>
+      </c>
+      <c r="N9" s="5">
+        <v>61</v>
+      </c>
+      <c r="O9" s="5">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="11" ht="34" customHeight="1">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>Kassa 世界赛数据</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="12" ht="34" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>赛段</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>选手</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Games</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Kills</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Assists</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Deaths</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>KA/D</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Dmg dealt</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>Dmg taken</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>Dmg diff</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>Dmg dealt/Games</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>Carry Value</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>Player Value</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>场均伤害排名（本次比赛）</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>参赛选手人数</t>
         </is>
-      </c>
-    </row>
-    <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Y4-S2 Playoffs</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Kassa</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="n">
-        <v>34</v>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>36</v>
-      </c>
-      <c r="G12" s="6" t="n">
-        <v>1.861111111111111</v>
-      </c>
-      <c r="H12" s="5" t="n">
-        <v>17681</v>
-      </c>
-      <c r="I12" s="5" t="n">
-        <v>16791</v>
-      </c>
-      <c r="J12" s="5" t="n">
-        <v>890</v>
-      </c>
-      <c r="K12" s="6" t="n">
-        <v>520.0294117647059</v>
-      </c>
-      <c r="L12" s="6" t="n">
-        <v>-36.62</v>
-      </c>
-      <c r="M12" s="6" t="n">
-        <v>-17.13</v>
-      </c>
-      <c r="N12" s="5" t="n">
-        <v>75</v>
-      </c>
-      <c r="O12" s="5" t="n">
-        <v>123</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Y4-Championship</t>
+          <t>Y4-S2 Playoffs</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -3745,49 +3847,49 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>1.823529411764706</v>
+        <v>1.861111111111111</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>30972</v>
+        <v>17681</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>30866</v>
+        <v>16791</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>106</v>
+        <v>890</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>720.2790697674419</v>
+        <v>520.0294117647059</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>13.44</v>
+        <v>-36.62</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>5.58</v>
+        <v>-17.13</v>
       </c>
       <c r="N13" s="5" t="n">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="O13" s="5" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Y5-S1 Open</t>
+          <t>Y4-Championship</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -3796,49 +3898,49 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>1.511111111111111</v>
+        <v>1.823529411764706</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>21873</v>
+        <v>30972</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>25987</v>
+        <v>30866</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>-4114</v>
+        <v>106</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>607.5833333333334</v>
+        <v>720.2790697674419</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>-8.449999999999999</v>
+        <v>13.44</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>-4.32</v>
+        <v>5.58</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>189</v>
+        <v>57</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>448</v>
+        <v>120</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Y5-S1 Playoffs/EWC</t>
+          <t>Y5-S1 Open</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -3847,49 +3949,49 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>3.125</v>
+        <v>1.511111111111111</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>13896</v>
+        <v>21873</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>13128</v>
+        <v>25987</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>768</v>
+        <v>-4114</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>731.3684210526316</v>
+        <v>607.5833333333334</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>5.24</v>
+        <v>-8.449999999999999</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>14.15</v>
+        <v>-4.32</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>26</v>
+        <v>189</v>
       </c>
       <c r="O15" s="5" t="n">
-        <v>120</v>
+        <v>448</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Y5-Championship</t>
+          <t>Y5-S1 Playoffs/EWC</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -3898,40 +4000,40 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>1.085714285714286</v>
+        <v>3.125</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>15777</v>
+        <v>13896</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>17561</v>
+        <v>13128</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>-1784</v>
+        <v>768</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>525.9</v>
+        <v>731.3684210526316</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>-17.86</v>
+        <v>5.24</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>-27.27</v>
+        <v>14.15</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>98</v>
+        <v>26</v>
       </c>
       <c r="O16" s="5" t="n">
         <v>120</v>
@@ -3940,56 +4042,107 @@
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
+          <t>Y5-Championship</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Kassa</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>1.085714285714286</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>15777</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>17561</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>-1784</v>
+      </c>
+      <c r="K17" s="6" t="n">
+        <v>525.9</v>
+      </c>
+      <c r="L17" s="6" t="n">
+        <v>-17.86</v>
+      </c>
+      <c r="M17" s="6" t="n">
+        <v>-27.27</v>
+      </c>
+      <c r="N17" s="5" t="n">
+        <v>98</v>
+      </c>
+      <c r="O17" s="5" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
           <t>Y6-S1 Playoffs</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>Kassa</t>
         </is>
       </c>
-      <c r="C17" s="5" t="n">
+      <c r="C18" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="D17" s="5" t="n">
+      <c r="D18" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="E17" s="5" t="n">
+      <c r="E18" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="F17" s="5" t="n">
+      <c r="F18" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="G17" s="6" t="n">
+      <c r="G18" s="6" t="n">
         <v>1.793103448275862</v>
       </c>
-      <c r="H17" s="5" t="n">
+      <c r="H18" s="5" t="n">
         <v>27298</v>
       </c>
-      <c r="I17" s="5" t="n">
+      <c r="I18" s="5" t="n">
         <v>26752</v>
       </c>
-      <c r="J17" s="5" t="n">
+      <c r="J18" s="5" t="n">
         <v>546</v>
       </c>
-      <c r="K17" s="6" t="n">
+      <c r="K18" s="6" t="n">
         <v>974.9285714285714</v>
       </c>
-      <c r="L17" s="6" t="n">
+      <c r="L18" s="6" t="n">
         <v>-1.56</v>
       </c>
-      <c r="M17" s="6" t="n">
+      <c r="M18" s="6" t="n">
         <v>7.62</v>
       </c>
-      <c r="N17" s="5" t="n">
+      <c r="N18" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="O17" s="5" t="n">
+      <c r="O18" s="5" t="n">
         <v>121</v>
       </c>
     </row>
-    <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>排名口径：按每个赛段该次比赛的全部参赛选手，以累计伤害 / Games 计算场均伤害并降序排名。</t>
         </is>
@@ -3997,9 +4150,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A10:O10"/>
+    <mergeCell ref="A11:O11"/>
     <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A19:O19"/>
+    <mergeCell ref="A20:O20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -4016,7 +4169,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:O20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -4375,145 +4528,145 @@
         <v>97</v>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="1" t="inlineStr">
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>APAC-S Y6-Split2</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>QQ</t>
+        </is>
+      </c>
+      <c r="C8" s="5">
+        <v>45</v>
+      </c>
+      <c r="D8" s="5">
+        <v>82</v>
+      </c>
+      <c r="E8" s="5">
+        <v>79</v>
+      </c>
+      <c r="F8" s="5">
+        <v>42</v>
+      </c>
+      <c r="G8" s="6">
+        <v>3.8333333333333335</v>
+      </c>
+      <c r="H8" s="5">
+        <v>48629</v>
+      </c>
+      <c r="I8" s="5">
+        <v>36776</v>
+      </c>
+      <c r="J8" s="5">
+        <v>11853</v>
+      </c>
+      <c r="K8" s="6">
+        <v>1080.6444444444444</v>
+      </c>
+      <c r="L8" s="6">
+        <v>21.84</v>
+      </c>
+      <c r="M8" s="6">
+        <v>55.04</v>
+      </c>
+      <c r="N8" s="5">
+        <v>4</v>
+      </c>
+      <c r="O8" s="5">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="10" ht="34" customHeight="1">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>QQ 世界赛数据</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="11" ht="34" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>赛段</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>选手</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>Games</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Kills</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Assists</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Deaths</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>KA/D</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Dmg dealt</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>Dmg taken</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>Dmg diff</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>Dmg dealt/Games</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>Carry Value</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>Player Value</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>场均伤害排名（本次比赛）</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>参赛选手人数</t>
         </is>
-      </c>
-    </row>
-    <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Y4-S1 Playoffs</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>QQ</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="n">
-        <v>24</v>
-      </c>
-      <c r="D11" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="E11" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="F11" s="5" t="n">
-        <v>24</v>
-      </c>
-      <c r="G11" s="6" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="H11" s="5" t="n">
-        <v>9366</v>
-      </c>
-      <c r="I11" s="5" t="n">
-        <v>9014</v>
-      </c>
-      <c r="J11" s="5" t="n">
-        <v>352</v>
-      </c>
-      <c r="K11" s="6" t="n">
-        <v>390.25</v>
-      </c>
-      <c r="L11" s="6" t="n">
-        <v>35.46</v>
-      </c>
-      <c r="M11" s="6" t="n">
-        <v>-22.38</v>
-      </c>
-      <c r="N11" s="5" t="n">
-        <v>94</v>
-      </c>
-      <c r="O11" s="5" t="n">
-        <v>120</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Y4-S2 Playoffs</t>
+          <t>Y4-S1 Playoffs</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -4522,49 +4675,49 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>1.885714285714286</v>
+        <v>0.875</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>21572</v>
+        <v>9366</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>19106</v>
+        <v>9014</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>2466</v>
+        <v>352</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>634.4705882352941</v>
+        <v>390.25</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>4.66</v>
+        <v>35.46</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>10.39</v>
+        <v>-22.38</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>36</v>
+        <v>94</v>
       </c>
       <c r="O12" s="5" t="n">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Y4-Championship</t>
+          <t>Y4-S2 Playoffs</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -4573,49 +4726,49 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>2.047619047619047</v>
+        <v>1.885714285714286</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>32119</v>
+        <v>21572</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>32012</v>
+        <v>19106</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>107</v>
+        <v>2466</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>746.953488372093</v>
+        <v>634.4705882352941</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>5.75</v>
+        <v>4.66</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.46</v>
+        <v>10.39</v>
       </c>
       <c r="N13" s="5" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="O13" s="5" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Y5-S1 Open</t>
+          <t>Y4-Championship</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -4624,49 +4777,49 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>1.594594594594595</v>
+        <v>2.047619047619047</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>26919</v>
+        <v>32119</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>24073</v>
+        <v>32012</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>2846</v>
+        <v>107</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>747.75</v>
+        <v>746.953488372093</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>15.3</v>
+        <v>5.75</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>11.51</v>
+        <v>0.46</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>79</v>
+        <v>47</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>448</v>
+        <v>120</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Y5-S1 Playoffs/EWC</t>
+          <t>Y5-S1 Open</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -4675,49 +4828,49 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>2.666666666666667</v>
+        <v>1.594594594594595</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>11898</v>
+        <v>26919</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>14578</v>
+        <v>24073</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>-2680</v>
+        <v>2846</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>626.2105263157895</v>
+        <v>747.75</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>-7.38</v>
+        <v>15.3</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>5.74</v>
+        <v>11.51</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="O15" s="5" t="n">
-        <v>120</v>
+        <v>448</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Y5-Championship</t>
+          <t>Y5-S1 Playoffs/EWC</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -4726,40 +4879,40 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>1.303030303030303</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>18103</v>
+        <v>11898</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>20232</v>
+        <v>14578</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>-2129</v>
+        <v>-2680</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>603.4333333333333</v>
+        <v>626.2105263157895</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>0.25</v>
+        <v>-7.38</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>-15.19</v>
+        <v>5.74</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>77</v>
+        <v>43</v>
       </c>
       <c r="O16" s="5" t="n">
         <v>120</v>
@@ -4768,56 +4921,107 @@
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
+          <t>Y5-Championship</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>QQ</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>1.303030303030303</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>18103</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>20232</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>-2129</v>
+      </c>
+      <c r="K17" s="6" t="n">
+        <v>603.4333333333333</v>
+      </c>
+      <c r="L17" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M17" s="6" t="n">
+        <v>-15.19</v>
+      </c>
+      <c r="N17" s="5" t="n">
+        <v>77</v>
+      </c>
+      <c r="O17" s="5" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
           <t>Y6-S1 Playoffs</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>QQ</t>
         </is>
       </c>
-      <c r="C17" s="5" t="n">
+      <c r="C18" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="D17" s="5" t="n">
+      <c r="D18" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="E17" s="5" t="n">
+      <c r="E18" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="F17" s="5" t="n">
+      <c r="F18" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="G17" s="6" t="n">
+      <c r="G18" s="6" t="n">
         <v>2.071428571428572</v>
       </c>
-      <c r="H17" s="5" t="n">
+      <c r="H18" s="5" t="n">
         <v>23872</v>
       </c>
-      <c r="I17" s="5" t="n">
+      <c r="I18" s="5" t="n">
         <v>24965</v>
       </c>
-      <c r="J17" s="5" t="n">
+      <c r="J18" s="5" t="n">
         <v>-1093</v>
       </c>
-      <c r="K17" s="6" t="n">
+      <c r="K18" s="6" t="n">
         <v>852.5714285714286</v>
       </c>
-      <c r="L17" s="6" t="n">
+      <c r="L18" s="6" t="n">
         <v>-0.95</v>
       </c>
-      <c r="M17" s="6" t="n">
+      <c r="M18" s="6" t="n">
         <v>8.02</v>
       </c>
-      <c r="N17" s="5" t="n">
+      <c r="N18" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="O17" s="5" t="n">
+      <c r="O18" s="5" t="n">
         <v>121</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>排名口径：按每个赛段该次比赛的全部参赛选手，以累计伤害 / Games 计算场均伤害并降序排名。</t>
         </is>
@@ -4826,8 +5030,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A9:O9"/>
-    <mergeCell ref="A19:O19"/>
+    <mergeCell ref="A10:O10"/>
+    <mergeCell ref="A20:O20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -4844,7 +5048,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O16"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -5152,145 +5356,145 @@
         <v>97</v>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
-      <c r="A8" s="1" t="inlineStr">
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>APAC-S Y6-Split2</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Noname</t>
+        </is>
+      </c>
+      <c r="C7" s="5">
+        <v>45</v>
+      </c>
+      <c r="D7" s="5">
+        <v>81</v>
+      </c>
+      <c r="E7" s="5">
+        <v>50</v>
+      </c>
+      <c r="F7" s="5">
+        <v>45</v>
+      </c>
+      <c r="G7" s="6">
+        <v>2.911111111111111</v>
+      </c>
+      <c r="H7" s="5">
+        <v>48403</v>
+      </c>
+      <c r="I7" s="5">
+        <v>37089</v>
+      </c>
+      <c r="J7" s="5">
+        <v>11314</v>
+      </c>
+      <c r="K7" s="6">
+        <v>1075.6222222222223</v>
+      </c>
+      <c r="L7" s="6">
+        <v>32.64</v>
+      </c>
+      <c r="M7" s="6">
+        <v>56.3</v>
+      </c>
+      <c r="N7" s="5">
+        <v>5</v>
+      </c>
+      <c r="O7" s="5">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="9" ht="34" customHeight="1">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>Noname 世界赛数据</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="10" ht="34" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>赛段</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>选手</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Games</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Kills</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Assists</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Deaths</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>KA/D</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Dmg dealt</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>Dmg taken</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>Dmg diff</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>Dmg dealt/Games</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>Carry Value</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>Player Value</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>场均伤害排名（本次比赛）</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>参赛选手人数</t>
         </is>
-      </c>
-    </row>
-    <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Y4-S2 Playoffs</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Noname</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="n">
-        <v>34</v>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>58</v>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>34</v>
-      </c>
-      <c r="G10" s="6" t="n">
-        <v>2.529411764705882</v>
-      </c>
-      <c r="H10" s="5" t="n">
-        <v>29009</v>
-      </c>
-      <c r="I10" s="5" t="n">
-        <v>21011</v>
-      </c>
-      <c r="J10" s="5" t="n">
-        <v>7998</v>
-      </c>
-      <c r="K10" s="6" t="n">
-        <v>853.2058823529412</v>
-      </c>
-      <c r="L10" s="6" t="n">
-        <v>63.32</v>
-      </c>
-      <c r="M10" s="6" t="n">
-        <v>53.42</v>
-      </c>
-      <c r="N10" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="O10" s="5" t="n">
-        <v>123</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Y4-Championship</t>
+          <t>Y4-S2 Playoffs</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -5299,49 +5503,49 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>12</v>
+        <v>58</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>1.666666666666667</v>
+        <v>2.529411764705882</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>20346</v>
+        <v>29009</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>13722</v>
+        <v>21011</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>6624</v>
+        <v>7998</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>782.5384615384615</v>
+        <v>853.2058823529412</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>26.59</v>
+        <v>63.32</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>-3.88</v>
+        <v>53.42</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="O11" s="5" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Y5-S1 Playoffs/EWC</t>
+          <t>Y4-Championship</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -5350,40 +5554,40 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D12" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="F12" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="E12" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>20</v>
-      </c>
       <c r="G12" s="6" t="n">
-        <v>2.4</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>20215</v>
+        <v>20346</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>14016</v>
+        <v>13722</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>6199</v>
+        <v>6624</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>1063.947368421053</v>
+        <v>782.5384615384615</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>46.76</v>
+        <v>26.59</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>49.66</v>
+        <v>-3.88</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="O12" s="5" t="n">
         <v>120</v>
@@ -5392,7 +5596,7 @@
     <row r="13" ht="24" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Y5-Championship</t>
+          <t>Y5-S1 Playoffs/EWC</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -5401,40 +5605,40 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="E13" s="5" t="n">
         <v>21</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>2.433333333333333</v>
+        <v>2.4</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>30564</v>
+        <v>20215</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>22298</v>
+        <v>14016</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>8266</v>
+        <v>6199</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>1018.8</v>
+        <v>1063.947368421053</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>65.51000000000001</v>
+        <v>46.76</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>57.88</v>
+        <v>49.66</v>
       </c>
       <c r="N13" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O13" s="5" t="n">
         <v>120</v>
@@ -5443,56 +5647,107 @@
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
+          <t>Y5-Championship</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Noname</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>2.433333333333333</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>30564</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>22298</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>8266</v>
+      </c>
+      <c r="K14" s="6" t="n">
+        <v>1018.8</v>
+      </c>
+      <c r="L14" s="6" t="n">
+        <v>65.51000000000001</v>
+      </c>
+      <c r="M14" s="6" t="n">
+        <v>57.88</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="O14" s="5" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
           <t>Y6-S1 Playoffs</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Noname</t>
         </is>
       </c>
-      <c r="C14" s="5" t="n">
+      <c r="C15" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="D14" s="5" t="n">
+      <c r="D15" s="5" t="n">
         <v>44</v>
       </c>
-      <c r="E14" s="5" t="n">
+      <c r="E15" s="5" t="n">
         <v>39</v>
       </c>
-      <c r="F14" s="5" t="n">
+      <c r="F15" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="G14" s="6" t="n">
+      <c r="G15" s="6" t="n">
         <v>2.371428571428571</v>
       </c>
-      <c r="H14" s="5" t="n">
+      <c r="H15" s="5" t="n">
         <v>44283</v>
       </c>
-      <c r="I14" s="5" t="n">
+      <c r="I15" s="5" t="n">
         <v>28577</v>
       </c>
-      <c r="J14" s="5" t="n">
+      <c r="J15" s="5" t="n">
         <v>15706</v>
       </c>
-      <c r="K14" s="6" t="n">
+      <c r="K15" s="6" t="n">
         <v>1165.342105263158</v>
       </c>
-      <c r="L14" s="6" t="n">
+      <c r="L15" s="6" t="n">
         <v>31.89</v>
       </c>
-      <c r="M14" s="6" t="n">
+      <c r="M15" s="6" t="n">
         <v>48.32</v>
       </c>
-      <c r="N14" s="5" t="n">
+      <c r="N15" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="O14" s="5" t="n">
+      <c r="O15" s="5" t="n">
         <v>121</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>排名口径：按每个赛段该次比赛的全部参赛选手，以累计伤害 / Games 计算场均伤害并降序排名。</t>
         </is>
@@ -5501,8 +5756,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A8:O8"/>
-    <mergeCell ref="A16:O16"/>
+    <mergeCell ref="A9:O9"/>
+    <mergeCell ref="A17:O17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -5519,7 +5774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O16"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -5929,145 +6184,145 @@
         <v>97</v>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
-      <c r="A10" s="1" t="inlineStr">
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>APAC-S Y6-Split2</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>bolin</t>
+        </is>
+      </c>
+      <c r="C9" s="5">
+        <v>45</v>
+      </c>
+      <c r="D9" s="5">
+        <v>29</v>
+      </c>
+      <c r="E9" s="5">
+        <v>34</v>
+      </c>
+      <c r="F9" s="5">
+        <v>50</v>
+      </c>
+      <c r="G9" s="6">
+        <v>1.26</v>
+      </c>
+      <c r="H9" s="5">
+        <v>31855</v>
+      </c>
+      <c r="I9" s="5">
+        <v>30402</v>
+      </c>
+      <c r="J9" s="5">
+        <v>1453</v>
+      </c>
+      <c r="K9" s="6">
+        <v>707.8888888888889</v>
+      </c>
+      <c r="L9" s="6">
+        <v>-0.59</v>
+      </c>
+      <c r="M9" s="6">
+        <v>-4.12</v>
+      </c>
+      <c r="N9" s="5">
+        <v>33</v>
+      </c>
+      <c r="O9" s="5">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="11" ht="34" customHeight="1">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>bolin 世界赛数据</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="12" ht="34" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>赛段</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>选手</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Games</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Kills</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Assists</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Deaths</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>KA/D</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Dmg dealt</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>Dmg taken</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>Dmg diff</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>Dmg dealt/Games</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>Carry Value</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>Player Value</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>场均伤害排名（本次比赛）</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>参赛选手人数</t>
         </is>
-      </c>
-    </row>
-    <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Y4-S1 Playoffs</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>bolin</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>32</v>
-      </c>
-      <c r="G12" s="6" t="n">
-        <v>1.125</v>
-      </c>
-      <c r="H12" s="5" t="n">
-        <v>10908</v>
-      </c>
-      <c r="I12" s="5" t="n">
-        <v>12302</v>
-      </c>
-      <c r="J12" s="5" t="n">
-        <v>-1394</v>
-      </c>
-      <c r="K12" s="6" t="n">
-        <v>363.6</v>
-      </c>
-      <c r="L12" s="6" t="n">
-        <v>-16.6</v>
-      </c>
-      <c r="M12" s="6" t="n">
-        <v>-28.13</v>
-      </c>
-      <c r="N12" s="5" t="n">
-        <v>109</v>
-      </c>
-      <c r="O12" s="5" t="n">
-        <v>120</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Y4-S2 Playoffs</t>
+          <t>Y4-S1 Playoffs</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -6076,98 +6331,149 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>1</v>
+        <v>1.125</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>4332</v>
+        <v>10908</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>2517</v>
+        <v>12302</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>1815</v>
+        <v>-1394</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>722</v>
+        <v>363.6</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>14.99</v>
+        <v>-16.6</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>17.18</v>
+        <v>-28.13</v>
       </c>
       <c r="N13" s="5" t="n">
-        <v>19</v>
+        <v>109</v>
       </c>
       <c r="O13" s="5" t="n">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
+          <t>Y4-S2 Playoffs</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>bolin</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>4332</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>2517</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>1815</v>
+      </c>
+      <c r="K14" s="6" t="n">
+        <v>722</v>
+      </c>
+      <c r="L14" s="6" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="M14" s="6" t="n">
+        <v>17.18</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="O14" s="5" t="n">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
           <t>Y5-S1 Open</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>bolin</t>
         </is>
       </c>
-      <c r="C14" s="5" t="n">
+      <c r="C15" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="D14" s="5" t="n">
+      <c r="D15" s="5" t="n">
         <v>48</v>
       </c>
-      <c r="E14" s="5" t="n">
+      <c r="E15" s="5" t="n">
         <v>44</v>
       </c>
-      <c r="F14" s="5" t="n">
+      <c r="F15" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="G14" s="6" t="n">
+      <c r="G15" s="6" t="n">
         <v>2.967741935483871</v>
       </c>
-      <c r="H14" s="5" t="n">
+      <c r="H15" s="5" t="n">
         <v>21778</v>
       </c>
-      <c r="I14" s="5" t="n">
+      <c r="I15" s="5" t="n">
         <v>16651</v>
       </c>
-      <c r="J14" s="5" t="n">
+      <c r="J15" s="5" t="n">
         <v>5127</v>
       </c>
-      <c r="K14" s="6" t="n">
+      <c r="K15" s="6" t="n">
         <v>725.9333333333333</v>
       </c>
-      <c r="L14" s="6" t="n">
+      <c r="L15" s="6" t="n">
         <v>14.85</v>
       </c>
-      <c r="M14" s="6" t="n">
+      <c r="M15" s="6" t="n">
         <v>33.07</v>
       </c>
-      <c r="N14" s="5" t="n">
+      <c r="N15" s="5" t="n">
         <v>91</v>
       </c>
-      <c r="O14" s="5" t="n">
+      <c r="O15" s="5" t="n">
         <v>448</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>排名口径：按每个赛段该次比赛的全部参赛选手，以累计伤害 / Games 计算场均伤害并降序排名。</t>
         </is>
@@ -6175,9 +6481,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A10:O10"/>
+    <mergeCell ref="A11:O11"/>
     <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A16:O16"/>
+    <mergeCell ref="A17:O17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -6194,7 +6500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O16"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -6553,145 +6859,145 @@
         <v>97</v>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="1" t="inlineStr">
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>APAC-S Y6-Split2</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>JackieChan</t>
+        </is>
+      </c>
+      <c r="C8" s="5">
+        <v>45</v>
+      </c>
+      <c r="D8" s="5">
+        <v>65</v>
+      </c>
+      <c r="E8" s="5">
+        <v>77</v>
+      </c>
+      <c r="F8" s="5">
+        <v>46</v>
+      </c>
+      <c r="G8" s="6">
+        <v>3.0869565217391304</v>
+      </c>
+      <c r="H8" s="5">
+        <v>44632</v>
+      </c>
+      <c r="I8" s="5">
+        <v>30519</v>
+      </c>
+      <c r="J8" s="5">
+        <v>14113</v>
+      </c>
+      <c r="K8" s="6">
+        <v>991.8222222222222</v>
+      </c>
+      <c r="L8" s="6">
+        <v>31.6</v>
+      </c>
+      <c r="M8" s="6">
+        <v>44.62</v>
+      </c>
+      <c r="N8" s="5">
+        <v>8</v>
+      </c>
+      <c r="O8" s="5">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="10" ht="34" customHeight="1">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>JackieChan 世界赛数据</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="11" ht="34" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>赛段</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>选手</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>Games</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Kills</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Assists</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Deaths</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>KA/D</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Dmg dealt</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>Dmg taken</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>Dmg diff</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>Dmg dealt/Games</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>Carry Value</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>Player Value</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>场均伤害排名（本次比赛）</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>参赛选手人数</t>
         </is>
-      </c>
-    </row>
-    <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Y4-S1 EWC</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>JackieChan</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="D11" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E11" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="F11" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="G11" s="6" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H11" s="5" t="n">
-        <v>9978</v>
-      </c>
-      <c r="I11" s="5" t="n">
-        <v>7800</v>
-      </c>
-      <c r="J11" s="5" t="n">
-        <v>2178</v>
-      </c>
-      <c r="K11" s="6" t="n">
-        <v>498.9</v>
-      </c>
-      <c r="L11" s="6" t="n">
-        <v>13.93</v>
-      </c>
-      <c r="M11" s="6" t="n">
-        <v>-5.1</v>
-      </c>
-      <c r="N11" s="5" t="n">
-        <v>77</v>
-      </c>
-      <c r="O11" s="5" t="n">
-        <v>120</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Y4-S2 Playoffs</t>
+          <t>Y4-S1 EWC</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -6700,49 +7006,49 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D12" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E12" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="E12" s="5" t="n">
-        <v>47</v>
-      </c>
       <c r="F12" s="5" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>2.193548387096774</v>
+        <v>1.8</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>12042</v>
+        <v>9978</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>11634</v>
+        <v>7800</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>408</v>
+        <v>2178</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>401.4</v>
+        <v>498.9</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>-16.27</v>
+        <v>13.93</v>
       </c>
       <c r="M12" s="6" t="n">
-        <v>-19.55</v>
+        <v>-5.1</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="O12" s="5" t="n">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Y4-Championship</t>
+          <t>Y4-S2 Playoffs</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -6751,98 +7057,149 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>1.423076923076923</v>
+        <v>2.193548387096774</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>13886</v>
+        <v>12042</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>15628</v>
+        <v>11634</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>-1742</v>
+        <v>408</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>534.0769230769231</v>
+        <v>401.4</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>-4.01</v>
+        <v>-16.27</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>-29.6</v>
+        <v>-19.55</v>
       </c>
       <c r="N13" s="5" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O13" s="5" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
+          <t>Y4-Championship</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>JackieChan</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>1.423076923076923</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>13886</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>15628</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>-1742</v>
+      </c>
+      <c r="K14" s="6" t="n">
+        <v>534.0769230769231</v>
+      </c>
+      <c r="L14" s="6" t="n">
+        <v>-4.01</v>
+      </c>
+      <c r="M14" s="6" t="n">
+        <v>-29.6</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>104</v>
+      </c>
+      <c r="O14" s="5" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
           <t>Y6-S1 Playoffs</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>JackieChan</t>
         </is>
       </c>
-      <c r="C14" s="5" t="n">
+      <c r="C15" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="D14" s="5" t="n">
+      <c r="D15" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="E14" s="5" t="n">
+      <c r="E15" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="F14" s="5" t="n">
+      <c r="F15" s="5" t="n">
         <v>32</v>
       </c>
-      <c r="G14" s="6" t="n">
+      <c r="G15" s="6" t="n">
         <v>1.40625</v>
       </c>
-      <c r="H14" s="5" t="n">
+      <c r="H15" s="5" t="n">
         <v>24805</v>
       </c>
-      <c r="I14" s="5" t="n">
+      <c r="I15" s="5" t="n">
         <v>23048</v>
       </c>
-      <c r="J14" s="5" t="n">
+      <c r="J15" s="5" t="n">
         <v>1757</v>
       </c>
-      <c r="K14" s="6" t="n">
+      <c r="K15" s="6" t="n">
         <v>885.8928571428571</v>
       </c>
-      <c r="L14" s="6" t="n">
+      <c r="L15" s="6" t="n">
         <v>19.43</v>
       </c>
-      <c r="M14" s="6" t="n">
+      <c r="M15" s="6" t="n">
         <v>5.05</v>
       </c>
-      <c r="N14" s="5" t="n">
+      <c r="N15" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="O14" s="5" t="n">
+      <c r="O15" s="5" t="n">
         <v>121</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>排名口径：按每个赛段该次比赛的全部参赛选手，以累计伤害 / Games 计算场均伤害并降序排名。</t>
         </is>
@@ -6851,8 +7208,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A9:O9"/>
-    <mergeCell ref="A16:O16"/>
+    <mergeCell ref="A10:O10"/>
+    <mergeCell ref="A17:O17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -6869,7 +7226,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -7075,143 +7432,194 @@
         <v>97</v>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
-      <c r="A6" s="1" t="inlineStr">
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>APAC-S Y6-Split2</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Return</t>
+        </is>
+      </c>
+      <c r="C5" s="5">
+        <v>45</v>
+      </c>
+      <c r="D5" s="5">
+        <v>51</v>
+      </c>
+      <c r="E5" s="5">
+        <v>43</v>
+      </c>
+      <c r="F5" s="5">
+        <v>48</v>
+      </c>
+      <c r="G5" s="6">
+        <v>1.9583333333333333</v>
+      </c>
+      <c r="H5" s="5">
+        <v>44307</v>
+      </c>
+      <c r="I5" s="5">
+        <v>35021</v>
+      </c>
+      <c r="J5" s="5">
+        <v>9286</v>
+      </c>
+      <c r="K5" s="6">
+        <v>984.6</v>
+      </c>
+      <c r="L5" s="6">
+        <v>37.57</v>
+      </c>
+      <c r="M5" s="6">
+        <v>29.86</v>
+      </c>
+      <c r="N5" s="5">
+        <v>9</v>
+      </c>
+      <c r="O5" s="5">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Return 世界赛数据</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="8" ht="34" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>赛段</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>选手</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Games</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Kills</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Assists</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Deaths</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>KA/D</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Dmg dealt</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>Dmg taken</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>Dmg diff</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>Dmg dealt/Games</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>Carry Value</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>Player Value</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>场均伤害排名（本次比赛）</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>参赛选手人数</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Y5-S1 Playoffs/EWC</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Return</t>
         </is>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C9" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="D8" s="5" t="n">
+      <c r="D9" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E8" s="5" t="n">
+      <c r="E9" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="F9" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="G8" s="6" t="n">
+      <c r="G9" s="6" t="n">
         <v>0.7272727272727273</v>
       </c>
-      <c r="H8" s="5" t="n">
+      <c r="H9" s="5" t="n">
         <v>3334</v>
       </c>
-      <c r="I8" s="5" t="n">
+      <c r="I9" s="5" t="n">
         <v>4530</v>
       </c>
-      <c r="J8" s="5" t="n">
+      <c r="J9" s="5" t="n">
         <v>-1196</v>
       </c>
-      <c r="K8" s="6" t="n">
+      <c r="K9" s="6" t="n">
         <v>333.4</v>
       </c>
-      <c r="L8" s="6" t="n">
+      <c r="L9" s="6" t="n">
         <v>-8.23</v>
       </c>
-      <c r="M8" s="6" t="n">
+      <c r="M9" s="6" t="n">
         <v>-41.7</v>
       </c>
-      <c r="N8" s="5" t="n">
+      <c r="N9" s="5" t="n">
         <v>114</v>
       </c>
-      <c r="O8" s="5" t="n">
+      <c r="O9" s="5" t="n">
         <v>120</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>排名口径：按每个赛段该次比赛的全部参赛选手，以累计伤害 / Games 计算场均伤害并降序排名。</t>
         </is>
@@ -7219,9 +7627,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A10:O10"/>
+    <mergeCell ref="A11:O11"/>
     <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A6:O6"/>
+    <mergeCell ref="A7:O7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -8219,7 +8627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -8629,145 +9037,145 @@
         <v>97</v>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
-      <c r="A10" s="1" t="inlineStr">
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>APAC-S Y6-Split2</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>WenXx</t>
+        </is>
+      </c>
+      <c r="C9" s="5">
+        <v>45</v>
+      </c>
+      <c r="D9" s="5">
+        <v>77</v>
+      </c>
+      <c r="E9" s="5">
+        <v>77</v>
+      </c>
+      <c r="F9" s="5">
+        <v>48</v>
+      </c>
+      <c r="G9" s="6">
+        <v>3.2083333333333335</v>
+      </c>
+      <c r="H9" s="5">
+        <v>53043</v>
+      </c>
+      <c r="I9" s="5">
+        <v>35919</v>
+      </c>
+      <c r="J9" s="5">
+        <v>17124</v>
+      </c>
+      <c r="K9" s="6">
+        <v>1178.7333333333333</v>
+      </c>
+      <c r="L9" s="6">
+        <v>31.52</v>
+      </c>
+      <c r="M9" s="6">
+        <v>61.49</v>
+      </c>
+      <c r="N9" s="5">
+        <v>2</v>
+      </c>
+      <c r="O9" s="5">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="11" ht="34" customHeight="1">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>WenXx 世界赛数据</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="12" ht="34" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>赛段</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>选手</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Games</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Kills</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Assists</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Deaths</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>KA/D</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Dmg dealt</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>Dmg taken</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>Dmg diff</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>Dmg dealt/Games</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>Carry Value</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>Player Value</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>场均伤害排名（本次比赛）</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>参赛选手人数</t>
         </is>
-      </c>
-    </row>
-    <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Y4-S2 Playoffs</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>WenXx</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="G12" s="6" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="H12" s="5" t="n">
-        <v>16225</v>
-      </c>
-      <c r="I12" s="5" t="n">
-        <v>14193</v>
-      </c>
-      <c r="J12" s="5" t="n">
-        <v>2032</v>
-      </c>
-      <c r="K12" s="6" t="n">
-        <v>540.8333333333334</v>
-      </c>
-      <c r="L12" s="6" t="n">
-        <v>19.03</v>
-      </c>
-      <c r="M12" s="6" t="n">
-        <v>-5.49</v>
-      </c>
-      <c r="N12" s="5" t="n">
-        <v>68</v>
-      </c>
-      <c r="O12" s="5" t="n">
-        <v>123</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Y5-S1 Playoffs/EWC</t>
+          <t>Y4-S2 Playoffs</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -8776,49 +9184,49 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>2.421052631578947</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>16927</v>
+        <v>16225</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>13145</v>
+        <v>14193</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>3782</v>
+        <v>2032</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>890.8947368421053</v>
+        <v>540.8333333333334</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>22.74</v>
+        <v>19.03</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>33.65</v>
+        <v>-5.49</v>
       </c>
       <c r="N13" s="5" t="n">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="O13" s="5" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Y5-Championship</t>
+          <t>Y5-S1 Playoffs/EWC</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -8827,40 +9235,40 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="D14" s="5" t="n">
         <v>25</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>1.612903225806452</v>
+        <v>2.421052631578947</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>25612</v>
+        <v>16927</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>20342</v>
+        <v>13145</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>5270</v>
+        <v>3782</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>853.7333333333333</v>
+        <v>890.8947368421053</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>0.48</v>
+        <v>22.74</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>14.53</v>
+        <v>33.65</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="O14" s="5" t="n">
         <v>120</v>
@@ -8869,56 +9277,107 @@
     <row r="15" ht="24" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
+          <t>Y5-Championship</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>WenXx</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>1.612903225806452</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>25612</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>20342</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>5270</v>
+      </c>
+      <c r="K15" s="6" t="n">
+        <v>853.7333333333333</v>
+      </c>
+      <c r="L15" s="6" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="M15" s="6" t="n">
+        <v>14.53</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="O15" s="5" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
           <t>Y6-S1 Playoffs</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>WenXx</t>
         </is>
       </c>
-      <c r="C15" s="5" t="n">
+      <c r="C16" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="D15" s="5" t="n">
+      <c r="D16" s="5" t="n">
         <v>48</v>
       </c>
-      <c r="E15" s="5" t="n">
+      <c r="E16" s="5" t="n">
         <v>34</v>
       </c>
-      <c r="F15" s="5" t="n">
+      <c r="F16" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="G15" s="6" t="n">
+      <c r="G16" s="6" t="n">
         <v>2.277777777777778</v>
       </c>
-      <c r="H15" s="5" t="n">
+      <c r="H16" s="5" t="n">
         <v>42555</v>
       </c>
-      <c r="I15" s="5" t="n">
+      <c r="I16" s="5" t="n">
         <v>29720</v>
       </c>
-      <c r="J15" s="5" t="n">
+      <c r="J16" s="5" t="n">
         <v>12835</v>
       </c>
-      <c r="K15" s="6" t="n">
+      <c r="K16" s="6" t="n">
         <v>1119.868421052632</v>
       </c>
-      <c r="L15" s="6" t="n">
+      <c r="L16" s="6" t="n">
         <v>27.75</v>
       </c>
-      <c r="M15" s="6" t="n">
+      <c r="M16" s="6" t="n">
         <v>45.55</v>
       </c>
-      <c r="N15" s="5" t="n">
+      <c r="N16" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="O15" s="5" t="n">
+      <c r="O16" s="5" t="n">
         <v>121</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>排名口径：按每个赛段该次比赛的全部参赛选手，以累计伤害 / Games 计算场均伤害并降序排名。</t>
         </is>
@@ -8926,9 +9385,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A10:O10"/>
+    <mergeCell ref="A11:O11"/>
     <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A17:O17"/>
+    <mergeCell ref="A18:O18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
